--- a/tests/workbooktests/workbooks/test_swaption.xlsx
+++ b/tests/workbooktests/workbooks/test_swaption.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4531FEE4-F33B-4170-B5AD-8D2207EBFF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB1B487-BFA6-4740-BC2C-4D7AC76F4920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12120" yWindow="-19560" windowWidth="22185" windowHeight="16125" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
   </bookViews>
   <sheets>
     <sheet name="FixedFloatSwaption" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -199,7 +199,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -273,7 +273,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -632,27 +632,27 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R4C2YieldTermStructureHandle,A</v>
+      <c r="B4" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlEuribor("6M",B4)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R5C2Euribor,A</v>
+      <c r="B5" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B5" ca="1">_xll.qlEuribor("6M",B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -675,18 +675,18 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" cm="1">
-        <f t="array" ref="B9">_xll.qlCalendarAdvance2("Target",$B$2,B7,"ModifiedFollowing")</f>
-        <v>46905</v>
+      <c r="B9" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B7,"ModifiedFollowing")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" cm="1">
-        <f t="array" ref="B10">_xll.qlCalendarAdvance2("Target",$B$2,B8,"ModifiedFollowing")</f>
-        <v>48001</v>
+      <c r="B10" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B10" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B8,"ModifiedFollowing")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -701,74 +701,66 @@
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlMakeSchedule(B9,B10,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R12C2Schedule,A</v>
+      <c r="B12" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlMakeSchedule(B9,B10,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="str" cm="1">
-        <f t="array" ref="B13">_xll.qlMakeSchedule(B9,B10,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R13C2Schedule,A</v>
+      <c r="B13" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B13" ca="1">_xll.qlMakeSchedule(B9,B10,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="str" cm="1">
-        <f t="array" ref="B14">_xll.qlVanillaSwap("Payer",10000,B12,B11,"30/360",B13,B5,0,"Act/360")</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R14C2VanillaSwap,A</v>
+      <c r="B14" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlVanillaSwap("Payer",10000,B12,B11,"30/360",B13,B5,0,"Act/360")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="1">
-        <f t="array" ref="B16:B20">_xll.qlScheduleDates(B12) - 2</f>
-        <v>46903</v>
+      <c r="B16" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlScheduleDates(B12) - 2</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="1">
-        <v>46904</v>
-      </c>
+      <c r="B17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="1">
-        <v>47271</v>
-      </c>
+      <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="1">
-        <v>47635</v>
-      </c>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="4">
-        <v>47999</v>
-      </c>
+      <c r="B20" s="4"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="2" t="str" cm="1">
-        <f t="array" ref="B22">_xll.qlEuropeanExercise(B16)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R22C2EuropeanExercise,A</v>
+      <c r="B22" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlEuropeanExercise(B16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="2" t="str" cm="1">
-        <f t="array" ref="B23">_xll.qlBermudanExercise(B16:B19)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R23C2BermudanExercise,A</v>
+      <c r="B23" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBermudanExercise(B16:B19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -791,78 +783,78 @@
       <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="2" t="str" cm="1">
-        <f t="array" ref="B28">_xll.qlSwaption(B14,B22)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R28C2Swaption,A</v>
-      </c>
-      <c r="C28" s="2" t="str" cm="1">
-        <f t="array" ref="C28">_xll.qlSwaption(B14,B22,C25,C26)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R28C3Swaption,A</v>
+      <c r="B28" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B28" ca="1">_xll.qlSwaption(B14,B22)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C28" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C28" ca="1">_xll.qlSwaption(B14,B22,C25,C26)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="2" t="str" cm="1">
-        <f t="array" ref="B29">_xll.qlSwaption(B14,B23)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R29C2Swaption,A</v>
-      </c>
-      <c r="C29" s="2" t="str" cm="1">
-        <f t="array" ref="C29">_xll.qlSwaption(B14,B23,C25,C26)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R29C3Swaption,A</v>
+      <c r="B29" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B29" ca="1">_xll.qlSwaption(B14,B23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C29" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C29" ca="1">_xll.qlSwaption(B14,B23,C25,C26)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="2" t="str" cm="1">
-        <f t="array" ref="B31">_xll.qlSwaptionSettlementType(B28)</f>
-        <v>PHYSICAL</v>
-      </c>
-      <c r="C31" s="2" t="str" cm="1">
-        <f t="array" ref="C31">_xll.qlSwaptionSettlementType(C28)</f>
-        <v>CASH</v>
+      <c r="B31" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B31" ca="1">_xll.qlSwaptionSettlementType(B28)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C31" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C31" ca="1">_xll.qlSwaptionSettlementType(C28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="2" t="str" cm="1">
-        <f t="array" ref="B32">_xll.qlSwaptionSettlementMethod(B28)</f>
-        <v>PHYSICALOTC</v>
-      </c>
-      <c r="C32" s="2" t="str" cm="1">
-        <f t="array" ref="C32">_xll.qlSwaptionSettlementMethod(C28)</f>
-        <v>PARYIELDCURVE</v>
+      <c r="B32" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B32" ca="1">_xll.qlSwaptionSettlementMethod(B28)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C32" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C32" ca="1">_xll.qlSwaptionSettlementMethod(C28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="2" t="str" cm="1">
-        <f t="array" ref="B33">_xll.qlSwaptionType(B28)</f>
-        <v>PAYER</v>
-      </c>
-      <c r="C33" s="2" t="str" cm="1">
-        <f t="array" ref="C33">_xll.qlSwaptionType(C28)</f>
-        <v>PAYER</v>
+      <c r="B33" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B33" ca="1">_xll.qlSwaptionType(B28)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C33" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C33" ca="1">_xll.qlSwaptionType(C28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="str" cm="1">
-        <f t="array" ref="B34">_xll.qlSwaptionUnderlying(B28)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R34C2FixedVsFloatingSwap,A</v>
-      </c>
-      <c r="C34" s="2" t="str" cm="1">
-        <f t="array" ref="C34">_xll.qlSwaptionUnderlying(C28)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R34C3FixedVsFloatingSwap,A</v>
+      <c r="B34" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B34" ca="1">_xll.qlSwaptionUnderlying(B28)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C34" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C34" ca="1">_xll.qlSwaptionUnderlying(C28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -872,9 +864,9 @@
       <c r="A37" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="2" t="str" cm="1">
-        <f t="array" ref="B37">_xll.qlFlatForward(B2,0.025)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R37C2YieldTermStructureHandle,A</v>
+      <c r="B37" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B37" ca="1">_xll.qlFlatForward(B2,0.025)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -889,126 +881,126 @@
       <c r="A39" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="2" t="str" cm="1">
-        <f t="array" ref="B39">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B38,"act/365","Normal")</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R39C2SwaptionVolatilityStructureHandle,A</v>
+      <c r="B39" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B39" ca="1">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B38,"act/365","Normal")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="2" t="str" cm="1">
-        <f t="array" ref="B41">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R41C2BachelierSwaptionEngine,A</v>
-      </c>
-      <c r="C41" t="str" cm="1">
-        <f t="array" ref="C41">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R41C3BachelierSwaptionEngine,A</v>
+      <c r="B41" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B41" ca="1">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C41" t="e" cm="1">
+        <f t="array" aca="1" ref="C41" ca="1">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="2" t="str" cm="1">
-        <f t="array" ref="B42">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R42C2BachelierSwaptionEngine,A</v>
-      </c>
-      <c r="C42" t="str" cm="1">
-        <f t="array" ref="C42">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R42C3BachelierSwaptionEngine,A</v>
+      <c r="B42" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B42" ca="1">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C42" t="e" cm="1">
+        <f t="array" aca="1" ref="C42" ca="1">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="6" cm="1">
-        <f t="array" ref="B44">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B41))</f>
-        <v>128.29101161563773</v>
-      </c>
-      <c r="C44" s="6" cm="1">
-        <f t="array" ref="C44">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C41))</f>
-        <v>127.03485296074462</v>
+      <c r="B44" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B44" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B41))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C44" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C44" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C41))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="6" cm="1">
-        <f t="array" ref="B45">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B42))</f>
-        <v>128.29101161563773</v>
-      </c>
-      <c r="C45" s="6" cm="1">
-        <f t="array" ref="C45">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C42))</f>
-        <v>127.03485296074462</v>
+      <c r="B45" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B45" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B42))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C45" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C45" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C42))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="5" cm="1">
-        <f t="array" ref="B47">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"Normal")</f>
-        <v>8.000000000003938E-3</v>
-      </c>
-      <c r="C47" s="5" cm="1">
-        <f t="array" ref="C47">_xll.qlSwaptionImpliedVolatility(C28,C44,B37,0.01,,,,,"Normal")</f>
-        <v>8.0000000000039363E-3</v>
+      <c r="B47" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="B47" ca="1">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"Normal")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C47" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="C47" ca="1">_xll.qlSwaptionImpliedVolatility(C28,C44,B37,0.01,,,,,"Normal")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="6" cm="1">
-        <f t="array" ref="B48">_xll.qlSwaptionVega(B28,B44)</f>
-        <v>15310.148562733901</v>
-      </c>
-      <c r="C48" s="6" cm="1">
-        <f t="array" ref="C48">_xll.qlSwaptionVega(C28,C44)</f>
-        <v>15160.239575482346</v>
+      <c r="B48" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B48" ca="1">_xll.qlSwaptionVega(B28,B44)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C48" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C48" ca="1">_xll.qlSwaptionVega(C28,C44)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="6" cm="1">
-        <f t="array" ref="B49">_xll.qlSwaptionDelta(B28,B44)</f>
-        <v>13984.983628933902</v>
-      </c>
-      <c r="C49" s="6" cm="1">
-        <f t="array" ref="C49">_xll.qlSwaptionDelta(C28,C44)</f>
-        <v>13848.049965360837</v>
+      <c r="B49" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B49" ca="1">_xll.qlSwaptionDelta(B28,B44)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C49" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C49" ca="1">_xll.qlSwaptionDelta(C28,C44)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="6" cm="1">
-        <f t="array" ref="B50">_xll.qlSwaptionAnnuity(B28,B44)</f>
-        <v>27173.475726005141</v>
-      </c>
-      <c r="C50" s="6" cm="1">
-        <f t="array" ref="C50">_xll.qlSwaptionAnnuity(C28,C44)</f>
-        <v>26907.407228400523</v>
+      <c r="B50" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B50" ca="1">_xll.qlSwaptionAnnuity(B28,B44)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C50" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C50" ca="1">_xll.qlSwaptionAnnuity(C28,C44)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="6" cm="1">
-        <f t="array" ref="B51">_xll.qlSwaptionForwardPrice(B28,B44)</f>
-        <v>134.85939517514475</v>
-      </c>
-      <c r="C51" s="6" cm="1">
-        <f t="array" ref="C51">_xll.qlSwaptionForwardPrice(C28,C44)</f>
-        <v>133.53892233523567</v>
+      <c r="B51" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B51" ca="1">_xll.qlSwaptionForwardPrice(B28,B44)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C51" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C51" ca="1">_xll.qlSwaptionForwardPrice(C28,C44)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -1023,44 +1015,44 @@
       <c r="A54" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="7" cm="1">
-        <f t="array" ref="B54">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"ShiftedLogNormal",B53)</f>
-        <v>0.13306969341405267</v>
+      <c r="B54" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B54" ca="1">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"ShiftedLogNormal",B53)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="2" t="str" cm="1">
-        <f t="array" ref="B55">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B54,"act/365","ShiftedLogNormal",B53)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R55C2SwaptionVolatilityStructureHandle,A</v>
+      <c r="B55" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B55" ca="1">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B54,"act/365","ShiftedLogNormal",B53)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="2" t="str" cm="1">
-        <f t="array" ref="B57">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R57C2BlackSwaptionEngine,A</v>
-      </c>
-      <c r="C57" s="2" t="str" cm="1">
-        <f t="array" ref="C57">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R57C3BlackSwaptionEngine,A</v>
+      <c r="B57" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B57" ca="1">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C57" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C57" ca="1">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="2" t="str" cm="1">
-        <f t="array" ref="B58">_xll.qlBlackSwaptionEngine(B37,B55)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R58C2BlackSwaptionEngine,A</v>
-      </c>
-      <c r="C58" s="2" t="str" cm="1">
-        <f t="array" ref="C58">_xll.qlBlackSwaptionEngine(B37,B55)</f>
-        <v>欣[test_swaption.xlsx]Sheet1!R58C3BlackSwaptionEngine,A</v>
+      <c r="B58" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B58" ca="1">_xll.qlBlackSwaptionEngine(B37,B55)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C58" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C58" ca="1">_xll.qlBlackSwaptionEngine(B37,B55)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1070,26 +1062,26 @@
       <c r="A60" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="6" cm="1">
-        <f t="array" ref="B60">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B57))</f>
-        <v>128.29101161461412</v>
-      </c>
-      <c r="C60" s="6" cm="1">
-        <f t="array" ref="C60">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C57))</f>
-        <v>127.03485295973103</v>
+      <c r="B60" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B60" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B57))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C60" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C60" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C57))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="6" cm="1">
-        <f t="array" ref="B61">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B58))</f>
-        <v>128.29101161461412</v>
-      </c>
-      <c r="C61" s="6" cm="1">
-        <f t="array" ref="C61">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C58))</f>
-        <v>127.03485295973103</v>
+      <c r="B61" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B61" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B58))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C61" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="C61" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C58))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_swaption.xlsx
+++ b/tests/workbooktests/workbooks/test_swaption.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB1B487-BFA6-4740-BC2C-4D7AC76F4920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22745623-6AA2-43E5-B29C-0BA25D2F46A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
   </bookViews>
   <sheets>
     <sheet name="FixedFloatSwaption" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
   <si>
     <t>Evaluationdate</t>
   </si>
@@ -192,6 +192,93 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>swap_index</t>
+  </si>
+  <si>
+    <t>The swap index (e.g., USDLiborSwapIsdaFixAm).</t>
+  </si>
+  <si>
+    <t>option_tenor</t>
+  </si>
+  <si>
+    <t>The option tenor (as a qPeriod).</t>
+  </si>
+  <si>
+    <t>strike</t>
+  </si>
+  <si>
+    <t>The strike rate (optional).</t>
+  </si>
+  <si>
+    <t>nominal</t>
+  </si>
+  <si>
+    <t>The nominal amount (optional).</t>
+  </si>
+  <si>
+    <t>Settlement type ('Physical' or 'Cash') (optional).</t>
+  </si>
+  <si>
+    <t>Settlement method ('PhysicalOTC', 'PhysicalCleared', 'CollateralizedCashPrice', 'ParYieldCurve') (optional).</t>
+  </si>
+  <si>
+    <t>option_convention</t>
+  </si>
+  <si>
+    <t>The business day convention for option dates (optional).</t>
+  </si>
+  <si>
+    <t>exercise_date</t>
+  </si>
+  <si>
+    <t>The exercise date (optional).</t>
+  </si>
+  <si>
+    <t>underlying_type</t>
+  </si>
+  <si>
+    <t>The underlying swap type (optional).</t>
+  </si>
+  <si>
+    <t>exercise_calendar</t>
+  </si>
+  <si>
+    <t>The calendar for exercise dates (optional).</t>
+  </si>
+  <si>
+    <t>pricing_engine</t>
+  </si>
+  <si>
+    <t>The pricing engine (optional).</t>
+  </si>
+  <si>
+    <t>indexed_coupons</t>
+  </si>
+  <si>
+    <t>Whether to use indexed coupons (optional).</t>
+  </si>
+  <si>
+    <t>at_par_coupons</t>
+  </si>
+  <si>
+    <t>Whether to use at par coupons (optional).</t>
+  </si>
+  <si>
+    <t>MakeSwaption</t>
+  </si>
+  <si>
+    <t>10Y</t>
+  </si>
+  <si>
+    <t>CollateralizedCashPrice</t>
+  </si>
+  <si>
+    <t>Following</t>
+  </si>
+  <si>
+    <t>qlMakeSwaption</t>
   </si>
 </sst>
 </file>
@@ -201,7 +288,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +318,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -253,7 +348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -277,6 +372,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB17914-90B7-4F4C-8A77-9C3F50686491}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
@@ -632,27 +731,27 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
+      <c r="B2" s="1" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
-        <v>#VALUE!</v>
+      <c r="B4" s="2" t="str" cm="1">
+        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B5" ca="1">_xll.qlEuribor("6M",B4)</f>
-        <v>#VALUE!</v>
+      <c r="B5" s="2" t="str" cm="1">
+        <f t="array" ref="B5">_xll.qlEuribor("6M",B4)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R5C2Euribor,A</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -675,18 +774,18 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B9" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B7,"ModifiedFollowing")</f>
-        <v>#VALUE!</v>
+      <c r="B9" s="1" cm="1">
+        <f t="array" ref="B9">_xll.qlCalendarAdvance2("Target",$B$2,B7,"ModifiedFollowing")</f>
+        <v>46905</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B10" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B8,"ModifiedFollowing")</f>
-        <v>#VALUE!</v>
+      <c r="B10" s="1" cm="1">
+        <f t="array" ref="B10">_xll.qlCalendarAdvance2("Target",$B$2,B8,"ModifiedFollowing")</f>
+        <v>48001</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -701,66 +800,74 @@
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlMakeSchedule(B9,B10,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>#VALUE!</v>
+      <c r="B12" s="2" t="str" cm="1">
+        <f t="array" ref="B12">_xll.qlMakeSchedule(B9,B10,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R12C2Schedule,A</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlMakeSchedule(B9,B10,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>#VALUE!</v>
+      <c r="B13" s="2" t="str" cm="1">
+        <f t="array" ref="B13">_xll.qlMakeSchedule(B9,B10,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R13C2Schedule,A</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlVanillaSwap("Payer",10000,B12,B11,"30/360",B13,B5,0,"Act/360")</f>
-        <v>#VALUE!</v>
+      <c r="B14" s="2" t="str" cm="1">
+        <f t="array" ref="B14">_xll.qlVanillaSwap("Payer",10000,B12,B11,"30/360",B13,B5,0,"Act/360")</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R14C2VanillaSwap,A</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlScheduleDates(B12) - 2</f>
-        <v>#VALUE!</v>
+      <c r="B16" s="1" cm="1">
+        <f t="array" ref="B16:B20">_xll.qlScheduleDates(B12) - 2</f>
+        <v>46903</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="1"/>
+      <c r="B17" s="1">
+        <v>46904</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="1"/>
+      <c r="B18" s="1">
+        <v>47271</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="1"/>
+      <c r="B19" s="1">
+        <v>47635</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="4"/>
+      <c r="B20" s="4">
+        <v>47999</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.qlEuropeanExercise(B16)</f>
-        <v>#VALUE!</v>
+      <c r="B22" s="2" t="str" cm="1">
+        <f t="array" ref="B22">_xll.qlEuropeanExercise(B16)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R22C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBermudanExercise(B16:B19)</f>
-        <v>#VALUE!</v>
+      <c r="B23" s="2" t="str" cm="1">
+        <f t="array" ref="B23">_xll.qlBermudanExercise(B16:B19)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R23C2BermudanExercise,A</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -783,78 +890,78 @@
       <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B28" ca="1">_xll.qlSwaption(B14,B22)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C28" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C28" ca="1">_xll.qlSwaption(B14,B22,C25,C26)</f>
-        <v>#VALUE!</v>
+      <c r="B28" s="2" t="str" cm="1">
+        <f t="array" ref="B28">_xll.qlSwaption(B14,B22)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R28C2Swaption,A</v>
+      </c>
+      <c r="C28" s="2" t="str" cm="1">
+        <f t="array" ref="C28">_xll.qlSwaption(B14,B22,C25,C26)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R28C3Swaption,A</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B29" ca="1">_xll.qlSwaption(B14,B23)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C29" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C29" ca="1">_xll.qlSwaption(B14,B23,C25,C26)</f>
-        <v>#VALUE!</v>
+      <c r="B29" s="2" t="str" cm="1">
+        <f t="array" ref="B29">_xll.qlSwaption(B14,B23)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R29C2Swaption,A</v>
+      </c>
+      <c r="C29" s="2" t="str" cm="1">
+        <f t="array" ref="C29">_xll.qlSwaption(B14,B23,C25,C26)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R29C3Swaption,A</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B31" ca="1">_xll.qlSwaptionSettlementType(B28)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C31" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C31" ca="1">_xll.qlSwaptionSettlementType(C28)</f>
-        <v>#VALUE!</v>
+      <c r="B31" s="2" t="str" cm="1">
+        <f t="array" ref="B31">_xll.qlSwaptionSettlementType(B28)</f>
+        <v>PHYSICAL</v>
+      </c>
+      <c r="C31" s="2" t="str" cm="1">
+        <f t="array" ref="C31">_xll.qlSwaptionSettlementType(C28)</f>
+        <v>CASH</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B32" ca="1">_xll.qlSwaptionSettlementMethod(B28)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C32" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C32" ca="1">_xll.qlSwaptionSettlementMethod(C28)</f>
-        <v>#VALUE!</v>
+      <c r="B32" s="2" t="str" cm="1">
+        <f t="array" ref="B32">_xll.qlSwaptionSettlementMethod(B28)</f>
+        <v>PHYSICALOTC</v>
+      </c>
+      <c r="C32" s="2" t="str" cm="1">
+        <f t="array" ref="C32">_xll.qlSwaptionSettlementMethod(C28)</f>
+        <v>PARYIELDCURVE</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B33" ca="1">_xll.qlSwaptionType(B28)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C33" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C33" ca="1">_xll.qlSwaptionType(C28)</f>
-        <v>#VALUE!</v>
+      <c r="B33" s="2" t="str" cm="1">
+        <f t="array" ref="B33">_xll.qlSwaptionType(B28)</f>
+        <v>PAYER</v>
+      </c>
+      <c r="C33" s="2" t="str" cm="1">
+        <f t="array" ref="C33">_xll.qlSwaptionType(C28)</f>
+        <v>PAYER</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B34" ca="1">_xll.qlSwaptionUnderlying(B28)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C34" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C34" ca="1">_xll.qlSwaptionUnderlying(C28)</f>
-        <v>#VALUE!</v>
+      <c r="B34" s="2" t="str" cm="1">
+        <f t="array" ref="B34">_xll.qlSwaptionUnderlying(B28)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R34C2FixedVsFloatingSwap,A</v>
+      </c>
+      <c r="C34" s="2" t="str" cm="1">
+        <f t="array" ref="C34">_xll.qlSwaptionUnderlying(C28)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R34C3FixedVsFloatingSwap,A</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -864,9 +971,9 @@
       <c r="A37" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B37" ca="1">_xll.qlFlatForward(B2,0.025)</f>
-        <v>#VALUE!</v>
+      <c r="B37" s="2" t="str" cm="1">
+        <f t="array" ref="B37">_xll.qlFlatForward(B2,0.025)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R37C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -881,126 +988,126 @@
       <c r="A39" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B39" ca="1">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B38,"act/365","Normal")</f>
-        <v>#VALUE!</v>
+      <c r="B39" s="2" t="str" cm="1">
+        <f t="array" ref="B39">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B38,"act/365","Normal")</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R39C2SwaptionVolatilityStructureHandle,A</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B41" ca="1">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C41" t="e" cm="1">
-        <f t="array" aca="1" ref="C41" ca="1">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
-        <v>#VALUE!</v>
+      <c r="B41" s="2" t="str" cm="1">
+        <f t="array" ref="B41">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R41C2BachelierSwaptionEngine,A</v>
+      </c>
+      <c r="C41" t="str" cm="1">
+        <f t="array" ref="C41">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R41C3BachelierSwaptionEngine,A</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B42" ca="1">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C42" t="e" cm="1">
-        <f t="array" aca="1" ref="C42" ca="1">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
-        <v>#VALUE!</v>
+      <c r="B42" s="2" t="str" cm="1">
+        <f t="array" ref="B42">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R42C2BachelierSwaptionEngine,A</v>
+      </c>
+      <c r="C42" t="str" cm="1">
+        <f t="array" ref="C42">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R42C3BachelierSwaptionEngine,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B44" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B41))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C44" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C44" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C41))</f>
-        <v>#VALUE!</v>
+      <c r="B44" s="6" cm="1">
+        <f t="array" ref="B44">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B41))</f>
+        <v>128.29101161563773</v>
+      </c>
+      <c r="C44" s="6" cm="1">
+        <f t="array" ref="C44">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C41))</f>
+        <v>127.03485296074462</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B45" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B42))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C45" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C45" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C42))</f>
-        <v>#VALUE!</v>
+      <c r="B45" s="6" cm="1">
+        <f t="array" ref="B45">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B42))</f>
+        <v>128.29101161563773</v>
+      </c>
+      <c r="C45" s="6" cm="1">
+        <f t="array" ref="C45">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C42))</f>
+        <v>127.03485296074462</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="5" t="e" cm="1">
-        <f t="array" aca="1" ref="B47" ca="1">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"Normal")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C47" s="5" t="e" cm="1">
-        <f t="array" aca="1" ref="C47" ca="1">_xll.qlSwaptionImpliedVolatility(C28,C44,B37,0.01,,,,,"Normal")</f>
-        <v>#VALUE!</v>
+      <c r="B47" s="5" cm="1">
+        <f t="array" ref="B47">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"Normal")</f>
+        <v>8.000000000003938E-3</v>
+      </c>
+      <c r="C47" s="5" cm="1">
+        <f t="array" ref="C47">_xll.qlSwaptionImpliedVolatility(C28,C44,B37,0.01,,,,,"Normal")</f>
+        <v>8.0000000000039363E-3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B48" ca="1">_xll.qlSwaptionVega(B28,B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C48" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C48" ca="1">_xll.qlSwaptionVega(C28,C44)</f>
-        <v>#VALUE!</v>
+      <c r="B48" s="6" cm="1">
+        <f t="array" ref="B48">_xll.qlSwaptionVega(B28,B44)</f>
+        <v>15310.148562733901</v>
+      </c>
+      <c r="C48" s="6" cm="1">
+        <f t="array" ref="C48">_xll.qlSwaptionVega(C28,C44)</f>
+        <v>15160.239575482346</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B49" ca="1">_xll.qlSwaptionDelta(B28,B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C49" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C49" ca="1">_xll.qlSwaptionDelta(C28,C44)</f>
-        <v>#VALUE!</v>
+      <c r="B49" s="6" cm="1">
+        <f t="array" ref="B49">_xll.qlSwaptionDelta(B28,B44)</f>
+        <v>13984.983628933902</v>
+      </c>
+      <c r="C49" s="6" cm="1">
+        <f t="array" ref="C49">_xll.qlSwaptionDelta(C28,C44)</f>
+        <v>13848.049965360837</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B50" ca="1">_xll.qlSwaptionAnnuity(B28,B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C50" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C50" ca="1">_xll.qlSwaptionAnnuity(C28,C44)</f>
-        <v>#VALUE!</v>
+      <c r="B50" s="6" cm="1">
+        <f t="array" ref="B50">_xll.qlSwaptionAnnuity(B28,B44)</f>
+        <v>27173.475726005141</v>
+      </c>
+      <c r="C50" s="6" cm="1">
+        <f t="array" ref="C50">_xll.qlSwaptionAnnuity(C28,C44)</f>
+        <v>26907.407228400523</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B51" ca="1">_xll.qlSwaptionForwardPrice(B28,B44)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C51" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C51" ca="1">_xll.qlSwaptionForwardPrice(C28,C44)</f>
-        <v>#VALUE!</v>
+      <c r="B51" s="6" cm="1">
+        <f t="array" ref="B51">_xll.qlSwaptionForwardPrice(B28,B44)</f>
+        <v>134.85939517514475</v>
+      </c>
+      <c r="C51" s="6" cm="1">
+        <f t="array" ref="C51">_xll.qlSwaptionForwardPrice(C28,C44)</f>
+        <v>133.53892233523567</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -1015,44 +1122,44 @@
       <c r="A54" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B54" ca="1">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"ShiftedLogNormal",B53)</f>
-        <v>#VALUE!</v>
+      <c r="B54" s="7" cm="1">
+        <f t="array" ref="B54">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"ShiftedLogNormal",B53)</f>
+        <v>0.13306969341405267</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B55" ca="1">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B54,"act/365","ShiftedLogNormal",B53)</f>
-        <v>#VALUE!</v>
+      <c r="B55" s="2" t="str" cm="1">
+        <f t="array" ref="B55">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B54,"act/365","ShiftedLogNormal",B53)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R55C2SwaptionVolatilityStructureHandle,A</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B57" ca="1">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C57" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C57" ca="1">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
-        <v>#VALUE!</v>
+      <c r="B57" s="2" t="str" cm="1">
+        <f t="array" ref="B57">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R57C2BlackSwaptionEngine,A</v>
+      </c>
+      <c r="C57" s="2" t="str" cm="1">
+        <f t="array" ref="C57">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R57C3BlackSwaptionEngine,A</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B58" ca="1">_xll.qlBlackSwaptionEngine(B37,B55)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C58" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C58" ca="1">_xll.qlBlackSwaptionEngine(B37,B55)</f>
-        <v>#VALUE!</v>
+      <c r="B58" s="2" t="str" cm="1">
+        <f t="array" ref="B58">_xll.qlBlackSwaptionEngine(B37,B55)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R58C2BlackSwaptionEngine,A</v>
+      </c>
+      <c r="C58" s="2" t="str" cm="1">
+        <f t="array" ref="C58">_xll.qlBlackSwaptionEngine(B37,B55)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R58C3BlackSwaptionEngine,A</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1062,26 +1169,170 @@
       <c r="A60" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B60" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B57))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C60" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C60" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C57))</f>
-        <v>#VALUE!</v>
+      <c r="B60" s="6" cm="1">
+        <f t="array" ref="B60">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B57))</f>
+        <v>128.29101161461412</v>
+      </c>
+      <c r="C60" s="6" cm="1">
+        <f t="array" ref="C60">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C57))</f>
+        <v>127.03485295973103</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B61" ca="1">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B58))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C61" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="C61" ca="1">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C58))</f>
-        <v>#VALUE!</v>
+      <c r="B61" s="6" cm="1">
+        <f t="array" ref="B61">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B58))</f>
+        <v>128.29101161461412</v>
+      </c>
+      <c r="C61" s="6" cm="1">
+        <f t="array" ref="C61">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C58))</f>
+        <v>127.03485295973103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="2" t="str" cm="1">
+        <f t="array" ref="B66">_xll.qlEuriborSwapIsdaFixA("1y",B4,B37)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R82C2EuriborSwapIsdaFixA,A</v>
+      </c>
+      <c r="D66" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D68" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" s="2">
+        <v>10000</v>
+      </c>
+      <c r="D69" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>55</v>
+      </c>
+      <c r="B73" s="1">
+        <f>B2+365</f>
+        <v>46539</v>
+      </c>
+      <c r="D73" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>61</v>
+      </c>
+      <c r="D76" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="D77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="D78" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B79" s="9" t="str" cm="1">
+        <f t="array" ref="B79">_xll.qlMakeSwaption(B66,B67,B68,B69,B70,B71,B72,B73,,,,,,B2)</f>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R79C2Swaption,A</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_swaption.xlsx
+++ b/tests/workbooktests/workbooks/test_swaption.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22745623-6AA2-43E5-B29C-0BA25D2F46A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6C3088-3FEB-45C4-93ED-EA2438738610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
   </bookViews>
   <sheets>
     <sheet name="FixedFloatSwaption" sheetId="1" r:id="rId1"/>
@@ -775,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" cm="1">
-        <f t="array" ref="B9">_xll.qlCalendarAdvance2("Target",$B$2,B7,"ModifiedFollowing")</f>
+        <f t="array" ref="B9">_xll.qlCalendarAdvance("Target",$B$2,B7,"ModifiedFollowing")</f>
         <v>46905</v>
       </c>
     </row>
@@ -784,7 +784,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" cm="1">
-        <f t="array" ref="B10">_xll.qlCalendarAdvance2("Target",$B$2,B8,"ModifiedFollowing")</f>
+        <f t="array" ref="B10">_xll.qlCalendarAdvance("Target",$B$2,B8,"ModifiedFollowing")</f>
         <v>48001</v>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B66" s="2" t="str" cm="1">
         <f t="array" ref="B66">_xll.qlEuriborSwapIsdaFixA("1y",B4,B37)</f>
-        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R82C2EuriborSwapIsdaFixA,A</v>
+        <v>欣[test_swaption.xlsx]FixedFloatSwaption!R66C2EuriborSwapIsdaFixA,A</v>
       </c>
       <c r="D66" t="s">
         <v>44</v>
